--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ASH/adaptive/avg/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ASH/adaptive/avg/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -1243,6 +1243,191 @@
       <c r="K24" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=80,react_th=None,scale_th=1.0,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>90.86</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=1.0,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>84.81</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>38.53</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=90,react_th=None,scale_th=1.0,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=1.5,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=2.0,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>90.86</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=1.0,type=avg</t>
         </is>
       </c>
     </row>
